--- a/public/قالب-المعاملات.xlsx
+++ b/public/قالب-المعاملات.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33B3BD42-2592-4295-ADF4-976D3E1CCA93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61257376-565F-4D2E-8A1C-8C980B4DA6ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>اسم المقيم</t>
   </si>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t>رقم التأشيرة</t>
+  </si>
+  <si>
+    <t>رقم الحدود</t>
   </si>
 </sst>
 </file>
@@ -535,7 +538,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>17</v>

--- a/public/قالب-المعاملات.xlsx
+++ b/public/قالب-المعاملات.xlsx
@@ -3,19 +3,30 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61257376-565F-4D2E-8A1C-8C980B4DA6ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7AB42F4-28AF-4FB9-A9E4-7318A6776B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="المعاملات" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>اسم المقيم</t>
   </si>
@@ -72,13 +83,31 @@
   </si>
   <si>
     <t>رقم الحدود</t>
+  </si>
+  <si>
+    <t>تاريخ المعاملة</t>
+  </si>
+  <si>
+    <t>تاريخ انتهاء الإقامة</t>
+  </si>
+  <si>
+    <t>اسم الوسيط</t>
+  </si>
+  <si>
+    <t>رقم إقامة الوسيط</t>
+  </si>
+  <si>
+    <t>جوال الوسيط</t>
+  </si>
+  <si>
+    <t>رسوم الإقامة</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -91,6 +120,17 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="7">
@@ -153,7 +193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -172,6 +212,10 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -515,82 +559,220 @@
   <sheetPr>
     <tabColor rgb="FF2E86C1"/>
   </sheetPr>
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:Y10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="40.5546875" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="16.44140625" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="10" width="12" customWidth="1"/>
     <col min="11" max="12" width="10" customWidth="1"/>
-    <col min="13" max="14" width="12" customWidth="1"/>
-    <col min="15" max="18" width="15" customWidth="1"/>
-    <col min="19" max="19" width="30" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="14" max="15" width="10" customWidth="1"/>
+    <col min="16" max="20" width="12" customWidth="1"/>
+    <col min="21" max="24" width="15" customWidth="1"/>
+    <col min="25" max="25" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="L1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="R1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="U1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="V1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="W1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="X1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="Y1" s="6" t="s">
         <v>16</v>
       </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="X2" s="7"/>
+      <c r="Y2" s="7"/>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="X3" s="7"/>
+      <c r="Y3" s="7"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="8"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7"/>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7"/>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7"/>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="7"/>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7"/>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="X10" s="7"/>
+      <c r="Y10" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/قالب-المعاملات.xlsx
+++ b/public/قالب-المعاملات.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7AB42F4-28AF-4FB9-A9E4-7318A6776B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E73A774D-58C4-4FA9-974A-3869F12E9F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -133,7 +133,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -165,6 +165,12 @@
         <fgColor rgb="FF757575"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF36DABF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -193,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -217,12 +223,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF36DABF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -567,7 +581,7 @@
     <col min="3" max="3" width="18.109375" customWidth="1"/>
     <col min="4" max="4" width="16.44140625" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="16.44140625" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
     <col min="9" max="10" width="12" customWidth="1"/>
@@ -631,13 +645,13 @@
       <c r="Q1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="S1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="T1" s="9" t="s">
         <v>23</v>
       </c>
       <c r="U1" s="5" t="s">
@@ -659,6 +673,7 @@
     <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
+      <c r="F2" s="7"/>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
       <c r="J2" s="7"/>
@@ -671,6 +686,7 @@
     <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
+      <c r="F3" s="7"/>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="J3" s="7"/>
@@ -713,6 +729,7 @@
     <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
+      <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
       <c r="J6" s="7"/>
@@ -755,6 +772,7 @@
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
+      <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
       <c r="J9" s="7"/>
@@ -766,6 +784,7 @@
     <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
+      <c r="F10" s="7"/>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
       <c r="J10" s="7"/>
@@ -775,6 +794,12 @@
       <c r="Y10" s="7"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="خطأ في كتابة التواريخ" error="تحقق من تنسيق تواريخك" sqref="A2:A1048576 F2:F1048576" xr:uid="{2A93C3B2-F25B-4C5A-8434-97E84437E527}">
+      <formula1>43831</formula1>
+      <formula2>51136</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>

--- a/public/قالب-المعاملات.xlsx
+++ b/public/قالب-المعاملات.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E73A774D-58C4-4FA9-974A-3869F12E9F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDCE0A09-025E-49B1-94C6-12FC64E12E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>اسم المقيم</t>
   </si>
@@ -85,9 +85,6 @@
     <t>رقم الحدود</t>
   </si>
   <si>
-    <t>تاريخ المعاملة</t>
-  </si>
-  <si>
     <t>تاريخ انتهاء الإقامة</t>
   </si>
   <si>
@@ -101,6 +98,15 @@
   </si>
   <si>
     <t>رسوم الإقامة</t>
+  </si>
+  <si>
+    <t>تاريخ العملية</t>
+  </si>
+  <si>
+    <t>إصدار تأشيرة</t>
+  </si>
+  <si>
+    <t>كشف طبي</t>
   </si>
 </sst>
 </file>
@@ -573,7 +579,7 @@
   <sheetPr>
     <tabColor rgb="FF2E86C1"/>
   </sheetPr>
-  <dimension ref="A1:Y10"/>
+  <dimension ref="A1:AA10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.6640625" customWidth="1"/>
@@ -587,15 +593,15 @@
     <col min="9" max="10" width="12" customWidth="1"/>
     <col min="11" max="12" width="10" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="15" width="10" customWidth="1"/>
-    <col min="16" max="20" width="12" customWidth="1"/>
-    <col min="21" max="24" width="15" customWidth="1"/>
-    <col min="25" max="25" width="30" customWidth="1"/>
+    <col min="14" max="17" width="10" customWidth="1"/>
+    <col min="18" max="22" width="12" customWidth="1"/>
+    <col min="23" max="26" width="15" customWidth="1"/>
+    <col min="27" max="27" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -610,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>2</v>
@@ -628,49 +634,55 @@
         <v>6</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="N1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="P1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="T1" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="U1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="V1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="T1" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="U1" s="5" t="s">
+      <c r="W1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="X1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="Y1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="Z1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="AA1" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="F2" s="7"/>
@@ -680,10 +692,12 @@
       <c r="K2" s="7"/>
       <c r="L2" s="7"/>
       <c r="M2" s="7"/>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="7"/>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="Z2" s="7"/>
+      <c r="AA2" s="7"/>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="F3" s="7"/>
@@ -693,10 +707,12 @@
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="Z3" s="7"/>
+      <c r="AA3" s="7"/>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -708,10 +724,12 @@
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
       <c r="M4" s="7"/>
-      <c r="X4" s="7"/>
-      <c r="Y4" s="8"/>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="Z4" s="7"/>
+      <c r="AA4" s="8"/>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -723,10 +741,12 @@
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
       <c r="M5" s="7"/>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="7"/>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="Z5" s="7"/>
+      <c r="AA5" s="7"/>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="F6" s="7"/>
@@ -736,10 +756,12 @@
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
-      <c r="X6" s="7"/>
-      <c r="Y6" s="7"/>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="Z6" s="7"/>
+      <c r="AA6" s="7"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -751,10 +773,12 @@
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
       <c r="M7" s="7"/>
-      <c r="X7" s="7"/>
-      <c r="Y7" s="7"/>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="Z7" s="7"/>
+      <c r="AA7" s="7"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -766,10 +790,12 @@
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
-      <c r="X8" s="7"/>
-      <c r="Y8" s="7"/>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="Z8" s="7"/>
+      <c r="AA8" s="7"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="F9" s="7"/>
@@ -778,10 +804,11 @@
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
-      <c r="X9" s="7"/>
-      <c r="Y9" s="7"/>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="O9" s="7"/>
+      <c r="Z9" s="7"/>
+      <c r="AA9" s="7"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="F10" s="7"/>
@@ -790,8 +817,9 @@
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
-      <c r="X10" s="7"/>
-      <c r="Y10" s="7"/>
+      <c r="O10" s="7"/>
+      <c r="Z10" s="7"/>
+      <c r="AA10" s="7"/>
     </row>
   </sheetData>
   <dataValidations count="1">
